--- a/artfynd/A 45582-2025 artfynd.xlsx
+++ b/artfynd/A 45582-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>54789566</v>
       </c>
       <c r="B2" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>301755.0909498313</v>
+        <v>301755</v>
       </c>
       <c r="R2" t="n">
-        <v>6472532.835292596</v>
+        <v>6472533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2015-08-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -813,15 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102411316</v>
+        <v>102411384</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,38 +809,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>4786</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bokenäset, SÖ Hällebäck ca 400 m SÖ Kohagen, Boh</t>
+          <t>Bokenäset, SÖ Hällebäck ca 420 m SÖ Kohagen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>301755.0909498313</v>
+        <v>301787</v>
       </c>
       <c r="R3" t="n">
-        <v>6472532.835292596</v>
+        <v>6472559</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,24 +869,9 @@
           <t>2022-07-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Nära rylbeståndet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +891,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blandskog, talldominerad norr om. Yngre skog söder om stigen.</t>
+          <t>Äldre barrblandskog; vid stigkorsning</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102411384</v>
+        <v>102411316</v>
       </c>
       <c r="B4" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,37 +920,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4786</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius volemus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bokenäset, SÖ Hällebäck ca 420 m SÖ Kohagen, Boh</t>
+          <t>Bokenäset, SÖ Hällebäck ca 400 m SÖ Kohagen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>301786.9117649022</v>
+        <v>301755</v>
       </c>
       <c r="R4" t="n">
-        <v>6472558.045546065</v>
+        <v>6472533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,19 +981,14 @@
           <t>2022-07-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nära rylbeståndet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1008,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog; vid stigkorsning</t>
+          <t>Blandskog, talldominerad norr om. Yngre skog söder om stigen.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 45582-2025 artfynd.xlsx
+++ b/artfynd/A 45582-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54789566</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102411384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,8 +1038,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102411316</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>